--- a/testbuild/ValueSet-NoDomainVitalSignsBloodPressureMeasurementMethodValueSet.xlsx
+++ b/testbuild/ValueSet-NoDomainVitalSignsBloodPressureMeasurementMethodValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.2</t>
+    <t>0.6.0-alpha</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:31:28+00:00</t>
+    <t>2026-10-02T06:31:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/ValueSet-NoDomainVitalSignsBloodPressureMeasurementMethodValueSet.xlsx
+++ b/testbuild/ValueSet-NoDomainVitalSignsBloodPressureMeasurementMethodValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0-alpha</t>
+    <t>0.5.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T06:31:19+00:00</t>
+    <t>2026-10-02T08:56:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/ValueSet-NoDomainVitalSignsBloodPressureMeasurementMethodValueSet.xlsx
+++ b/testbuild/ValueSet-NoDomainVitalSignsBloodPressureMeasurementMethodValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.2</t>
+    <t>0.6.0-alpha</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T08:56:17+00:00</t>
+    <t>2026-10-02T09:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/ValueSet-NoDomainVitalSignsBloodPressureMeasurementMethodValueSet.xlsx
+++ b/testbuild/ValueSet-NoDomainVitalSignsBloodPressureMeasurementMethodValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T09:03:30+00:00</t>
+    <t>2026-10-02T10:19:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/ValueSet-NoDomainVitalSignsBloodPressureMeasurementMethodValueSet.xlsx
+++ b/testbuild/ValueSet-NoDomainVitalSignsBloodPressureMeasurementMethodValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T10:19:39+00:00</t>
+    <t>2026-10-02T10:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
